--- a/p6_deployment/data/italy/predicciones.xlsx
+++ b/p6_deployment/data/italy/predicciones.xlsx
@@ -609,26 +609,26 @@
         <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2687512367071206</v>
+        <v>0.2763914746914717</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3416109342541447</v>
+        <v>0.3563563441165634</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3896378290387348</v>
+        <v>0.3672521811919646</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0.08473173474973522</v>
+        <v>0.06234608690296495</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08473173474973522</v>
+        <v>0.06234608690296495</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3896378290387348</v>
+        <v>0.3672521811919646</v>
       </c>
       <c r="W2" t="n">
         <v>3.1</v>
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>19.48189145193674</v>
+        <v>18.36260905959823</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.48189145193674</v>
+        <v>18.36260905959823</v>
       </c>
     </row>
     <row r="3">
@@ -695,26 +695,26 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2235438090818182</v>
+        <v>0.2256767281456628</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3450144053254161</v>
+        <v>0.348253735631289</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4314417855927659</v>
+        <v>0.4260695362230483</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>0.1151852305302407</v>
+        <v>0.1098129811605231</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1151852305302407</v>
+        <v>0.1098129811605231</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4314417855927659</v>
+        <v>0.4260695362230483</v>
       </c>
       <c r="W3" t="n">
         <v>3</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>21.57208927963829</v>
+        <v>21.30347681115242</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.57208927963829</v>
+        <v>21.30347681115242</v>
       </c>
     </row>
     <row r="4">
@@ -781,26 +781,26 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6407642643527612</v>
+        <v>0.6433210241393781</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2942600841475537</v>
+        <v>0.2833053216314175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06497565149968521</v>
+        <v>0.07337365422920432</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-0.09040030065730542</v>
+        <v>-0.08784354087068857</v>
       </c>
       <c r="T4" t="n">
         <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09040030065730542</v>
+        <v>0.08784354087068857</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3592357356472388</v>
+        <v>0.3566789758606219</v>
       </c>
       <c r="W4" t="n">
         <v>3.508474576271186</v>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>17.96178678236194</v>
+        <v>17.83394879303109</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.96178678236194</v>
+        <v>17.83394879303109</v>
       </c>
     </row>
     <row r="5">
@@ -867,26 +867,26 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4348734207461024</v>
+        <v>0.4266061492187417</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3209426612703618</v>
+        <v>0.317368551131377</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2441839179835361</v>
+        <v>0.2560252996498812</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>0.284634554127026</v>
+        <v>0.2763672825996653</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.284634554127026</v>
+        <v>0.2763672825996653</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4348734207461024</v>
+        <v>0.4266061492187417</v>
       </c>
       <c r="W5" t="n">
         <v>6.25</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>21.74367103730512</v>
+        <v>21.33030746093709</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.74367103730512</v>
+        <v>21.33030746093709</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/italy/predicciones.xlsx
+++ b/p6_deployment/data/italy/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,100 +460,110 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>odds_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>odds_draw</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>odds_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_home_bm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_draw_bm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_away_bm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>predicted_result</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_class_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>copiado_formaciones</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -562,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4W5t03Zl</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45438.65625</v>
+        <v>45521.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -584,84 +594,96 @@
       <c r="F2" t="n">
         <v>771</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.7</v>
       </c>
-      <c r="I2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.439632042928325</v>
-      </c>
       <c r="K2" t="n">
-        <v>0.2554618627826753</v>
+        <v>1.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.1730133841070729</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.2571820574564596</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>0.5698045584364675</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2763914746914717</v>
+        <v>0.05089084729803295</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3563563441165634</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3672521811919646</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>0.1690231290469481</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5103258068256604</v>
+      </c>
       <c r="S2" t="n">
-        <v>0.06234608690296495</v>
+        <v>0.3206510641273914</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06234608690296495</v>
+        <v>0.2531437493692008</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3672521811919646</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
+        <v>0.2531437493692008</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.5103258068256604</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.36260905959823</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>18.36260905959823</v>
+        <v>3.7</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>20.51629034128302</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>20.51629034128302</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rN4paNle</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45438.65625</v>
+        <v>45521.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -670,84 +692,78 @@
       <c r="F3" t="n">
         <v>771</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J3" t="n">
         <v>3.2</v>
       </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.3872529245663574</v>
-      </c>
       <c r="K3" t="n">
-        <v>0.2964905203711174</v>
+        <v>2.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.2916584109371904</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.296215573608084</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0.4121260154547257</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2256767281456628</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.348253735631289</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.4260695362230483</v>
-      </c>
+        <v>0.05497491638795982</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0.1098129811605231</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1098129811605231</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4260695362230483</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>21.30347681115242</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>21.30347681115242</v>
-      </c>
+        <v>1.346846846846847</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6Le197C2</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45438.65625</v>
+        <v>45521.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -756,84 +772,96 @@
       <c r="F4" t="n">
         <v>771</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K4" t="n">
         <v>5.75</v>
       </c>
-      <c r="I4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.7311645650100667</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.1640351806718237</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1048002543181096</v>
+        <v>0.5657460116663153</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06021795303898436</v>
+        <v>0.2699416684236418</v>
       </c>
       <c r="N4" t="n">
+        <v>0.1643123199100429</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05842972440212746</v>
+      </c>
+      <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.6433210241393781</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.2833053216314175</v>
-      </c>
       <c r="Q4" t="n">
-        <v>0.07337365422920432</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>0.4915313988535168</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3362692658037094</v>
+      </c>
       <c r="S4" t="n">
-        <v>-0.08784354087068857</v>
+        <v>0.1721993353427739</v>
       </c>
       <c r="T4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08784354087068857</v>
+        <v>-0.07421461281279856</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3566789758606219</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>3.508474576271186</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
+        <v>-0.07421461281279856</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4915313988535168</v>
       </c>
       <c r="Y4" t="n">
-        <v>17.83394879303109</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17.83394879303109</v>
+        <v>1.67</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>19.57656994267584</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>19.57656994267584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jPP565dL</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45438.65625</v>
+        <v>45521.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -842,66 +870,1460 @@
       <c r="F5" t="n">
         <v>771</v>
       </c>
-      <c r="G5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.75</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1502388666190764</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1976827192356268</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6520784141452967</v>
+        <v>0.3774574049803408</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06497076023391823</v>
+        <v>0.2948885976408912</v>
       </c>
       <c r="N5" t="n">
+        <v>0.327653997378768</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05972222222222223</v>
+      </c>
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.4266061492187417</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.317368551131377</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.2560252996498812</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>0.3701517612699443</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3344432328435613</v>
+      </c>
       <c r="S5" t="n">
-        <v>0.2763672825996653</v>
+        <v>0.2954050058864942</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2763672825996653</v>
+        <v>-0.007305643710396492</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4266061492187417</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
+        <v>-0.007305643710396492</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.3701517612699443</v>
       </c>
       <c r="Y5" t="n">
-        <v>21.33030746093709</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>21.33030746093709</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>13.50758806349722</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13.50758806349722</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>771</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.511293669135136</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2702552251142862</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2184511057505777</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0572017084719163</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4660644204971483</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2688391176917718</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2650964618110795</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.04522924863798766</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.04522924863798766</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4660644204971483</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>18.30322102485741</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>18.30322102485741</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>771</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2259083728278041</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.287519747235387</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4865718799368088</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05394605394605412</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1547292148032319</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5385992929237166</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3066714922730516</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2510795456883296</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2510795456883296</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.5385992929237166</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>21.92996464618583</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21.92996464618583</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F8" t="n">
+        <v>771</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2489019033674963</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2781844802342606</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.472913616398243</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05727554179566563</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2078177782701987</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4621885313403238</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3299936903894771</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.1840040511060632</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1840040511060632</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.4621885313403238</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>18.10942656701619</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>18.10942656701619</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>771</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6380263717566993</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2360697575499787</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.125903870693322</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05900900900900896</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>1.236080178173719</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>catania</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="n">
+        <v>773</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mantova</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>773</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45508.54166666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>juve stabia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>avellino</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>773</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cesena</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>padova</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>773</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sassuolo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cittadella</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>773</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45513.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>reggiana</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>773</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sudtirol</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>773</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cremonese</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>bari</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>773</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>catanzaro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>773</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>modena</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>773</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>brescia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>773</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>palermo</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>773</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sampdoria</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>773</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cosenza</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>77</v>
+      </c>
+      <c r="F23" t="n">
+        <v>773</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>773</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>spezia</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>773</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/predicciones.xlsx
+++ b/p6_deployment/data/italy/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,42 +629,42 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1690231290469481</v>
+        <v>0.197446693092225</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5103258068256604</v>
+        <v>0.4912175511034044</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3206510641273914</v>
+        <v>0.3113357558043706</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2531437493692008</v>
+        <v>0.2340354936469448</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2531437493692008</v>
+        <v>0.2340354936469448</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5103258068256604</v>
+        <v>0.4912175511034044</v>
       </c>
       <c r="Y2" t="n">
         <v>3.7</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>20.51629034128302</v>
+        <v>14.73652653310213</v>
       </c>
       <c r="AB2" t="n">
-        <v>20.51629034128302</v>
+        <v>14.73652653310213</v>
       </c>
     </row>
     <row r="3">
@@ -741,7 +741,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr"/>
@@ -807,42 +807,42 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4915313988535168</v>
+        <v>0.4906362271247455</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3362692658037094</v>
+        <v>0.3879335704773906</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1721993353427739</v>
+        <v>0.1214302023978635</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07421461281279856</v>
+        <v>-0.07510978454156986</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.07421461281279856</v>
+        <v>-0.07510978454156986</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4915313988535168</v>
+        <v>0.4906362271247455</v>
       </c>
       <c r="Y4" t="n">
         <v>1.67</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>19.57656994267584</v>
+        <v>14.71908681374236</v>
       </c>
       <c r="AB4" t="n">
-        <v>19.57656994267584</v>
+        <v>14.71908681374236</v>
       </c>
     </row>
     <row r="5">
@@ -902,45 +902,45 @@
         <v>0.05972222222222223</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3701517612699443</v>
+        <v>0.3346715590221151</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3344432328435613</v>
+        <v>0.3283727881981005</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2954050058864942</v>
+        <v>0.3369556527797843</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.007305643710396492</v>
+        <v>0.009301655401016296</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.007305643710396492</v>
+        <v>0.009301655401016296</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3701517612699443</v>
+        <v>0.3369556527797843</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>13.50758806349722</v>
+        <v>10.10866958339353</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.50758806349722</v>
+        <v>10.10866958339353</v>
       </c>
     </row>
     <row r="6">
@@ -1003,42 +1003,42 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4660644204971483</v>
+        <v>0.381580524582578</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2688391176917718</v>
+        <v>0.3447478156195503</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2650964618110795</v>
+        <v>0.2736716597978718</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.04522924863798766</v>
+        <v>-0.1297131445525579</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.04522924863798766</v>
+        <v>0.1297131445525579</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4660644204971483</v>
+        <v>0.6184194754174219</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>1.935504469987229</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>18.30322102485741</v>
+        <v>18.55258426252266</v>
       </c>
       <c r="AB6" t="n">
-        <v>18.30322102485741</v>
+        <v>18.55258426252266</v>
       </c>
     </row>
     <row r="7">
@@ -1101,42 +1101,42 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1547292148032319</v>
+        <v>0.2089266748559978</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5385992929237166</v>
+        <v>0.4994075367830734</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3066714922730516</v>
+        <v>0.2916657883609288</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2510795456883296</v>
+        <v>0.2118877895476864</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2510795456883296</v>
+        <v>0.2118877895476864</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5385992929237166</v>
+        <v>0.4994075367830734</v>
       </c>
       <c r="Y7" t="n">
         <v>3.3</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>21.92996464618583</v>
+        <v>14.9822261034922</v>
       </c>
       <c r="AB7" t="n">
-        <v>21.92996464618583</v>
+        <v>14.9822261034922</v>
       </c>
     </row>
     <row r="8">
@@ -1199,42 +1199,42 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2078177782701987</v>
+        <v>0.218765794394865</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4621885313403238</v>
+        <v>0.460645745632017</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3299936903894771</v>
+        <v>0.3205884599731181</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1840040511060632</v>
+        <v>0.1824612653977564</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1840040511060632</v>
+        <v>0.1824612653977564</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4621885313403238</v>
+        <v>0.460645745632017</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.15</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>18.10942656701619</v>
+        <v>13.81937236896051</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.10942656701619</v>
+        <v>13.81937236896051</v>
       </c>
     </row>
     <row r="9">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -1320,27 +1320,27 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45507.54166666666</v>
+        <v>45523.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>carrarese</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>catania</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1349,60 +1349,96 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.23125</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05471324983520098</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2469107232017813</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3688299106034833</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3842593661947352</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.1282406338052647</v>
+      </c>
       <c r="V10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1282406338052647</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.6157406338052648</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.944871794871795</v>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>18.47221901415794</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>18.47221901415794</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45523.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UiGfvfvT</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>mantova</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>77</v>
       </c>
       <c r="F11" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1411,31 +1447,49 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7112375533428166</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.09957325746799432</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05714285714285694</v>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
         <v>-100</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>1.166666666666667</v>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -1444,20 +1498,20 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>f9bfyqFM</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45508.54166666666</v>
+        <v>45507.54166666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>carrarese</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>catania</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1497,7 +1551,7 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr"/>
@@ -1506,20 +1560,20 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>bHLf4sq9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45507.64583333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>UiGfvfvT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>padova</t>
+          <t>mantova</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1559,7 +1613,7 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -1568,20 +1622,20 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45508.54166666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>cittadella</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1611,9 +1665,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
         <v>-100</v>
@@ -1623,7 +1675,7 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -1632,20 +1684,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45508.64583333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>reggiana</t>
+          <t>padova</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1675,9 +1727,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
         <v>-100</v>
@@ -1687,7 +1737,7 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -1696,20 +1746,20 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45513.54166666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>sassuolo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sudtirol</t>
+          <t>cittadella</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1751,7 +1801,7 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
@@ -1760,20 +1810,20 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45514.54166666666</v>
+        <v>45513.65625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cremonese</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>bari</t>
+          <t>reggiana</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1803,7 +1853,9 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
         <v>-100</v>
@@ -1813,7 +1865,7 @@
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -1822,20 +1874,20 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45513.67708333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>catanzaro</t>
+          <t>sudtirol</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1877,7 +1929,7 @@
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr"/>
@@ -1886,20 +1938,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45514.54166666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>cremonese</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>modena</t>
+          <t>bari</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1929,9 +1981,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
         <v>-100</v>
@@ -1941,7 +1991,7 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -1950,20 +2000,20 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45514.65625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>brescia</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>catanzaro</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1993,7 +2043,9 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
         <v>-100</v>
@@ -2003,7 +2055,7 @@
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr"/>
@@ -2012,20 +2064,20 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45514.67708333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>palermo</t>
+          <t>modena</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2055,7 +2107,9 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
         <v>-100</v>
@@ -2065,7 +2119,7 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr"/>
@@ -2074,20 +2128,20 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45515.54166666666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>brescia</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2127,7 +2181,7 @@
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
@@ -2136,20 +2190,20 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45515.5625</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>cosenza</t>
+          <t>palermo</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2179,9 +2233,7 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
         <v>-100</v>
@@ -2191,7 +2243,7 @@
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -2200,20 +2252,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45515.65625</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>pisa</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2243,9 +2295,7 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
         <v>-100</v>
@@ -2255,7 +2305,7 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr"/>
@@ -2264,20 +2314,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45515.67708333334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>salernitana</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>spezia</t>
+          <t>cosenza</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2319,11 +2369,925 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.15</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>77</v>
+      </c>
+      <c r="F26" t="n">
+        <v>773</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>spezia</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>773</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>brescia</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>palermo</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>774</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.3387880751782242</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2892093324692158</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.37200259235256</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.05417776866844304</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>1.334579439252336</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>bari</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>juve stabia</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>77</v>
+      </c>
+      <c r="F29" t="n">
+        <v>774</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.4803482268595571</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.2830623479708104</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.2365894251696326</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.05142577157502526</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>1.3266</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>spezia</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>774</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.3674925475248008</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2962908664418707</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.3362165860333284</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.05470682830282048</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>1.347333333333333</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>cittadella</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>77</v>
+      </c>
+      <c r="F31" t="n">
+        <v>774</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5074481002161874</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.2779933070749548</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.2145585927088577</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.04266924809673589</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>1.328349056603773</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sudtirol</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>modena</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>77</v>
+      </c>
+      <c r="F32" t="n">
+        <v>774</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3578448399158204</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.301044071675214</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.3411110884089655</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.05453103824218264</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="n">
+        <v>1.356721915285451</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>catanzaro</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sassuolo</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>77</v>
+      </c>
+      <c r="F33" t="n">
+        <v>774</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.332488006590318</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.285418921320002</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.38209307208968</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.05530781871117751</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="n">
+        <v>1.326078799249531</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>cesena</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>77</v>
+      </c>
+      <c r="F34" t="n">
+        <v>774</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5010799503392914</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2759570740998997</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.2229629755608089</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.0503628994081784</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="n">
+        <v>1.314910858995138</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>cosenza</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>cremonese</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>77</v>
+      </c>
+      <c r="F35" t="n">
+        <v>774</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.30401160555386</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.2927865616564868</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.4032018327896534</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.05090993914300346</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="n">
+        <v>1.345500910746812</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>sampdoria</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>77</v>
+      </c>
+      <c r="F36" t="n">
+        <v>774</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.3720103701359559</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.2927859394588541</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.3352036904051899</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.05415572851310402</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="n">
+        <v>1.34135687732342</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>reggiana</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>mantova</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>77</v>
+      </c>
+      <c r="F37" t="n">
+        <v>774</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.3661612260661003</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.2927029554046913</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.3411358185292085</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.05445459162485533</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="n">
+        <v>1.340819366852886</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/predicciones.xlsx
+++ b/p6_deployment/data/italy/predicciones.xlsx
@@ -629,42 +629,42 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.197446693092225</v>
+        <v>0.2322024601791497</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4912175511034044</v>
+        <v>0.5231222758917055</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3113357558043706</v>
+        <v>0.2446752639291447</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2340354936469448</v>
+        <v>0.2659402184352458</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2340354936469448</v>
+        <v>0.2659402184352458</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4912175511034044</v>
+        <v>0.5231222758917055</v>
       </c>
       <c r="Y2" t="n">
         <v>3.7</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>14.73652653310213</v>
+        <v>15.69366827675116</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.73652653310213</v>
+        <v>15.69366827675116</v>
       </c>
     </row>
     <row r="3">
@@ -723,29 +723,47 @@
       <c r="O3" t="n">
         <v>0.05497491638795982</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2712172811525008</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.3960721730299201</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3327105458175788</v>
+      </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>0.09985659942183606</v>
+      </c>
       <c r="V3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.09985659942183606</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3960721730299201</v>
+      </c>
       <c r="Y3" t="n">
-        <v>1.346846846846847</v>
+        <v>3.2</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>11.8821651908976</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>11.8821651908976</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -804,45 +822,45 @@
         <v>0.05842972440212746</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4906362271247455</v>
+        <v>0.4372196027838811</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3879335704773906</v>
+        <v>0.5004885127723747</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1214302023978635</v>
+        <v>0.06229188444374419</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07510978454156986</v>
+        <v>0.2305468443487329</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.07510978454156986</v>
+        <v>0.2305468443487329</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4906362271247455</v>
+        <v>0.5004885127723747</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>14.71908681374236</v>
+        <v>15.01465538317124</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.71908681374236</v>
+        <v>15.01465538317124</v>
       </c>
     </row>
     <row r="5">
@@ -902,45 +920,45 @@
         <v>0.05972222222222223</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3346715590221151</v>
+        <v>0.3446007529713776</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3283727881981005</v>
+        <v>0.3526910107122487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3369556527797843</v>
+        <v>0.3027082363163736</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009301655401016296</v>
+        <v>0.05780241307135747</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.009301655401016296</v>
+        <v>0.05780241307135747</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3369556527797843</v>
+        <v>0.3526910107122487</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>10.10866958339353</v>
+        <v>10.58073032136746</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.10866958339353</v>
+        <v>10.58073032136746</v>
       </c>
     </row>
     <row r="6">
@@ -1003,42 +1021,42 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.381580524582578</v>
+        <v>0.4323588882589242</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3447478156195503</v>
+        <v>0.3773943291766955</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2736716597978718</v>
+        <v>0.1902467825643805</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1297131445525579</v>
+        <v>-0.07893478087621175</v>
       </c>
       <c r="V6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1297131445525579</v>
+        <v>-0.07893478087621175</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6184194754174219</v>
+        <v>0.4323588882589242</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.935504469987229</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>18.55258426252266</v>
+        <v>12.97076664776773</v>
       </c>
       <c r="AB6" t="n">
-        <v>18.55258426252266</v>
+        <v>12.97076664776773</v>
       </c>
     </row>
     <row r="7">
@@ -1101,42 +1119,42 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2089266748559978</v>
+        <v>0.2317021112264668</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4994075367830734</v>
+        <v>0.5192890211216494</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2916657883609288</v>
+        <v>0.2490088676518839</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2118877895476864</v>
+        <v>0.2317692738862625</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2118877895476864</v>
+        <v>0.2317692738862625</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4994075367830734</v>
+        <v>0.5192890211216494</v>
       </c>
       <c r="Y7" t="n">
         <v>3.3</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>14.9822261034922</v>
+        <v>15.57867063364948</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.9822261034922</v>
+        <v>15.57867063364948</v>
       </c>
     </row>
     <row r="8">
@@ -1175,66 +1193,66 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2489019033674963</v>
+        <v>0.2411347517730496</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2781844802342606</v>
+        <v>0.276595744680851</v>
       </c>
       <c r="N8" t="n">
-        <v>0.472913616398243</v>
+        <v>0.4822695035460993</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05727554179566563</v>
+        <v>0.06334841628959298</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.218765794394865</v>
+        <v>0.2446428108738779</v>
       </c>
       <c r="R8" t="n">
-        <v>0.460645745632017</v>
+        <v>0.4922937003799233</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3205884599731181</v>
+        <v>0.2630634887461985</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1824612653977564</v>
+        <v>0.2156979556990722</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1824612653977564</v>
+        <v>0.2156979556990722</v>
       </c>
       <c r="X8" t="n">
-        <v>0.460645745632017</v>
+        <v>0.4922937003799233</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>13.81937236896051</v>
+        <v>14.7688110113977</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.81937236896051</v>
+        <v>14.7688110113977</v>
       </c>
     </row>
     <row r="9">
@@ -1293,29 +1311,47 @@
       <c r="O9" t="n">
         <v>0.05900900900900896</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4672142682244892</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4687109776100618</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.06407475416544899</v>
+      </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>0.2326412200600831</v>
+      </c>
       <c r="V9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.2326412200600831</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4687109776100618</v>
+      </c>
       <c r="Y9" t="n">
-        <v>1.236080178173719</v>
+        <v>4</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>14.06132932830185</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>14.06132932830185</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1374,45 +1410,45 @@
         <v>0.05471324983520098</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2469107232017813</v>
+        <v>0.2655594552965543</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3688299106034833</v>
+        <v>0.405819549403178</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3842593661947352</v>
+        <v>0.3286209953002677</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1282406338052647</v>
+        <v>0.149569549403178</v>
       </c>
       <c r="V10" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1282406338052647</v>
+        <v>0.149569549403178</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6157406338052648</v>
+        <v>0.405819549403178</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.944871794871795</v>
+        <v>3.7</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>18.47221901415794</v>
+        <v>12.17458648209534</v>
       </c>
       <c r="AB10" t="n">
-        <v>18.47221901415794</v>
+        <v>12.17458648209534</v>
       </c>
     </row>
     <row r="11">
@@ -1471,29 +1507,47 @@
       <c r="O11" t="n">
         <v>0.05714285714285694</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4896822687582531</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4535486110547644</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.05676912018698233</v>
+      </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>-0.2215552845845635</v>
+      </c>
       <c r="V11" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.2215552845845635</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.4896822687582531</v>
+      </c>
       <c r="Y11" t="n">
-        <v>1.166666666666667</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>14.69046806274759</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>14.69046806274759</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1551,7 +1605,7 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr"/>
@@ -1613,7 +1667,7 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr"/>
@@ -1675,7 +1729,7 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr"/>
@@ -1737,7 +1791,7 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -1785,27 +1839,41 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4714480047822973</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4056032949254639</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1229487002922389</v>
+      </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>0.5285519952177027</v>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>15.85655985653108</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>15.85655985653108</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1849,27 +1917,41 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.474807650426295</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.4097372930966371</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.115455056477068</v>
+      </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.525192349573705</v>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>15.75577048721115</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>15.75577048721115</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1913,27 +1995,41 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4744099064021176</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3974162014452964</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.128173892152586</v>
+      </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>0.5255900935978823</v>
+      </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>15.76770280793647</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15.76770280793647</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1977,25 +2073,41 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3963285464173486</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3801911881083933</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2234802654742581</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="n">
+        <v>0.6036714535826514</v>
+      </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>18.11014360747954</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>18.11014360747954</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2039,27 +2151,41 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4357604694674418</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3721789459378736</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1920605845946844</v>
+      </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="n">
+        <v>0.5642395305325583</v>
+      </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>16.92718591597675</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16.92718591597675</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2103,10 +2229,18 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.4748223715979581</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.4821446094511965</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.04303301895084537</v>
+      </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
@@ -2115,15 +2249,21 @@
         <v>-100</v>
       </c>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>0.5178553905488035</v>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>15.53566171646411</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>15.53566171646411</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2167,25 +2307,41 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3378760736066398</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.35690813030224</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3052157960911198</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
         <v>-100</v>
       </c>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>0.64309186969776</v>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>19.2927560909328</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>19.2927560909328</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2229,25 +2385,41 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.4069732312491904</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3643269271489426</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.228699841601867</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="n">
+        <v>0.5930267687508096</v>
+      </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>17.79080306252429</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>17.79080306252429</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2291,25 +2463,41 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3694937315310033</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3732029792473935</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2573032892216031</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
         <v>-100</v>
       </c>
       <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>0.6267970207526066</v>
+      </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>18.8039106225782</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>18.8039106225782</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2353,27 +2541,41 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4733371806917877</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.4239851741582934</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1026776451499188</v>
+      </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="n">
+        <v>0.5266628193082123</v>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>15.79988457924637</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>15.79988457924637</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2417,27 +2619,41 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4238880895081383</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3826738469226045</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1934380635692574</v>
+      </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="n">
+        <v>0.5761119104918617</v>
+      </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>17.28335731475585</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>17.28335731475585</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2481,27 +2697,41 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.4544331171342493</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3913317838444145</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.1542350990213361</v>
+      </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="n">
+        <v>0.5455668828657507</v>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>16.36700648597252</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>16.36700648597252</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2559,27 +2789,47 @@
       <c r="O28" t="n">
         <v>0.05417776866844304</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.3380050469588385</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3739226193959451</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2880723336452164</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.08471328692672925</v>
+      </c>
       <c r="V28" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.08471328692672925</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.3739226193959451</v>
+      </c>
       <c r="Y28" t="n">
-        <v>1.334579439252336</v>
+        <v>3.28</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>11.21767858187835</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>11.21767858187835</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2641,7 +2891,9 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
         <v>-100</v>
@@ -2653,7 +2905,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr"/>
@@ -2715,27 +2967,47 @@
       <c r="O30" t="n">
         <v>0.05470682830282048</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.3790586940833662</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.3715543510497629</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.2493869548668708</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.01156614655856542</v>
+      </c>
       <c r="V30" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.01156614655856542</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.3790586940833662</v>
+      </c>
       <c r="Y30" t="n">
-        <v>1.347333333333333</v>
+        <v>2.58</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>11.37176082250099</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>11.37176082250099</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2773,49 +3045,67 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="K31" t="n">
-        <v>4.47</v>
+        <v>4.25</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5074481002161874</v>
+        <v>0.5001539461530566</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2779933070749548</v>
+        <v>0.276247819096165</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2145585927088577</v>
+        <v>0.2235982347507783</v>
       </c>
       <c r="O31" t="n">
-        <v>0.04266924809673589</v>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+        <v>0.05230758153934767</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.4583076869532984</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3950426087473192</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.146649704299382</v>
+      </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>-0.04184625919975826</v>
+      </c>
       <c r="V31" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.04184625919975826</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.4583076869532984</v>
+      </c>
       <c r="Y31" t="n">
-        <v>1.328349056603773</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>13.74923060859895</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>13.74923060859895</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2873,27 +3163,47 @@
       <c r="O32" t="n">
         <v>0.05453103824218264</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3614264383835507</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.3743785460922382</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.2641950155242111</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.07333447441702423</v>
+      </c>
       <c r="V32" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.07333447441702423</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.3743785460922382</v>
+      </c>
       <c r="Y32" t="n">
-        <v>1.356721915285451</v>
+        <v>3.15</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>11.23135638276715</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>11.23135638276715</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2931,49 +3241,67 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="J33" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="K33" t="n">
         <v>2.48</v>
       </c>
       <c r="L33" t="n">
-        <v>0.332488006590318</v>
+        <v>0.3338384652587457</v>
       </c>
       <c r="M33" t="n">
-        <v>0.285418921320002</v>
+        <v>0.2838626471062389</v>
       </c>
       <c r="N33" t="n">
-        <v>0.38209307208968</v>
+        <v>0.3822988876350153</v>
       </c>
       <c r="O33" t="n">
-        <v>0.05530781871117751</v>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+        <v>0.05473968011274155</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.3082132045474408</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.3596842295085814</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.3321025659439776</v>
+      </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>0.07582158240234249</v>
+      </c>
       <c r="V33" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.07582158240234249</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.3596842295085814</v>
+      </c>
       <c r="Y33" t="n">
-        <v>1.326078799249531</v>
+        <v>3.34</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>10.79052688525744</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>10.79052688525744</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3047,7 +3375,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr"/>
@@ -3089,47 +3417,67 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="J35" t="n">
         <v>3.25</v>
       </c>
       <c r="K35" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="L35" t="n">
-        <v>0.30401160555386</v>
+        <v>0.302817041016593</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2927865616564868</v>
+        <v>0.2925678488591084</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4032018327896534</v>
+        <v>0.4046151101242987</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05090993914300346</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+        <v>0.05169556016554244</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.3272688283754523</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.3746482331421275</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2980829384824198</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.08208038428301917</v>
+      </c>
       <c r="V35" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.08208038428301917</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.3746482331421275</v>
+      </c>
       <c r="Y35" t="n">
-        <v>1.345500910746812</v>
+        <v>3.25</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>11.23944699426383</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>11.23944699426383</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3187,29 +3535,47 @@
       <c r="O36" t="n">
         <v>0.05415572851310402</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.3943496459569794</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.3799057602844827</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.2257445937585379</v>
+      </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>0.02233927582102341</v>
+      </c>
       <c r="V36" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.02233927582102341</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.3943496459569794</v>
+      </c>
       <c r="Y36" t="n">
-        <v>1.34135687732342</v>
+        <v>2.55</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>11.83048937870938</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>11.83048937870938</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3271,7 +3637,9 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
         <v>-100</v>
@@ -3283,7 +3651,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>

--- a/p6_deployment/data/italy/predicciones.xlsx
+++ b/p6_deployment/data/italy/predicciones.xlsx
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1730133841070729</v>
+        <v>0.158004158004158</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2571820574564596</v>
+        <v>0.2494802494802495</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5698045584364675</v>
+        <v>0.5925155925155925</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05089084729803295</v>
+        <v>0.05482456140350878</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -641,19 +641,19 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2659402184352458</v>
+        <v>0.273642026411456</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2659402184352458</v>
+        <v>0.273642026411456</v>
       </c>
       <c r="X2" t="n">
         <v>0.5231222758917055</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>15.69366827675116</v>
+        <v>3.530708773348613</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.69366827675116</v>
+        <v>3.530708773348613</v>
       </c>
     </row>
     <row r="3">
@@ -703,52 +703,52 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2916584109371904</v>
+        <v>0.2858844550327576</v>
       </c>
       <c r="M3" t="n">
-        <v>0.296215573608084</v>
+        <v>0.2948183442525313</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4121260154547257</v>
+        <v>0.4192972007147112</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05497491638795982</v>
+        <v>0.0599747474747474</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2712172811525008</v>
+        <v>0.2711379192563951</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3960721730299201</v>
+        <v>0.3958014781491829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3327105458175788</v>
+        <v>0.3330606025944221</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09985659942183606</v>
+        <v>0.1009831338966516</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09985659942183606</v>
+        <v>0.1009831338966516</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3960721730299201</v>
+        <v>0.3958014781491829</v>
       </c>
       <c r="Y3" t="n">
         <v>3.2</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>11.8821651908976</v>
+        <v>2.671382611309341</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.8821651908976</v>
+        <v>2.671382611309341</v>
       </c>
     </row>
     <row r="4">
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5657460116663153</v>
+        <v>0.5439668439257036</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2699416684236418</v>
+        <v>0.2767831294092551</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1643123199100429</v>
+        <v>0.1792500266650414</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05842972440212746</v>
+        <v>0.06262851961593885</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -837,19 +837,19 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2305468443487329</v>
+        <v>0.2237053833631196</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2305468443487329</v>
+        <v>0.2237053833631196</v>
       </c>
       <c r="X4" t="n">
         <v>0.5004885127723747</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>15.01465538317124</v>
+        <v>3.377946733377945</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.01465538317124</v>
+        <v>3.377946733377945</v>
       </c>
     </row>
     <row r="5">
@@ -899,25 +899,25 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3774574049803408</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2948885976408912</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="N5" t="n">
-        <v>0.327653997378768</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05972222222222223</v>
+        <v>0.0625</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05780241307135747</v>
+        <v>0.05857336365342514</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05780241307135747</v>
+        <v>0.05857336365342514</v>
       </c>
       <c r="X5" t="n">
         <v>0.3526910107122487</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>10.58073032136746</v>
+        <v>2.380417166675411</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.58073032136746</v>
+        <v>2.380417166675411</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4323588882589242</v>
+        <v>0.4323588882589248</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3773943291766955</v>
+        <v>0.3773943291766953</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1902467825643805</v>
+        <v>0.19024678256438</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.07893478087621175</v>
+        <v>-0.07893478087621114</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.07893478087621175</v>
+        <v>-0.07893478087621114</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4323588882589242</v>
+        <v>0.4323588882589248</v>
       </c>
       <c r="Y6" t="n">
         <v>1.85</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>12.97076664776773</v>
+        <v>2.918119511177259</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.97076664776773</v>
+        <v>2.918119511177259</v>
       </c>
     </row>
     <row r="7">
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2317021112264668</v>
+        <v>0.2317021112264667</v>
       </c>
       <c r="R7" t="n">
         <v>0.5192890211216494</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>15.57867063364948</v>
+        <v>3.504836989884513</v>
       </c>
       <c r="AB7" t="n">
-        <v>15.57867063364948</v>
+        <v>3.504836989884513</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2446428108738779</v>
+        <v>0.2446428108738781</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4922937003799233</v>
+        <v>0.492293700379923</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2630634887461985</v>
+        <v>0.2630634887461987</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2156979556990722</v>
+        <v>0.215697955699072</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2156979556990722</v>
+        <v>0.215697955699072</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4922937003799233</v>
+        <v>0.492293700379923</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>14.7688110113977</v>
+        <v>3.322637492415771</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.7688110113977</v>
+        <v>3.322637492415771</v>
       </c>
     </row>
     <row r="9">
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>14.06132932830185</v>
+        <v>3.163470639807426</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.06132932830185</v>
+        <v>3.163470639807426</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2655594552965543</v>
+        <v>0.2653946255938225</v>
       </c>
       <c r="R10" t="n">
-        <v>0.405819549403178</v>
+        <v>0.406166107039758</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3286209953002677</v>
+        <v>0.3284392673664195</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.149569549403178</v>
+        <v>0.149916107039758</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.149569549403178</v>
+        <v>0.149916107039758</v>
       </c>
       <c r="X10" t="n">
-        <v>0.405819549403178</v>
+        <v>0.406166107039758</v>
       </c>
       <c r="Y10" t="n">
         <v>3.7</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>12.17458648209534</v>
+        <v>2.74133659308937</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.17458648209534</v>
+        <v>2.74133659308937</v>
       </c>
     </row>
     <row r="11">
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>14.69046806274759</v>
+        <v>3.305012158985048</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.69046806274759</v>
+        <v>3.305012158985048</v>
       </c>
     </row>
     <row r="12">
@@ -1843,13 +1843,13 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4714480047822973</v>
+        <v>0.4714480047822971</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4056032949254639</v>
+        <v>0.4056032949254636</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1229487002922389</v>
+        <v>0.1229487002922391</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>0.5285519952177027</v>
+        <v>0.5285519952177029</v>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>15.85655985653108</v>
+        <v>3.567355573809254</v>
       </c>
       <c r="AB16" t="n">
-        <v>15.85655985653108</v>
+        <v>3.567355573809254</v>
       </c>
     </row>
     <row r="17">
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>15.75577048721115</v>
+        <v>3.544680320054506</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.75577048721115</v>
+        <v>3.544680320054506</v>
       </c>
     </row>
     <row r="18">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>15.76770280793647</v>
+        <v>3.547364813490225</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.76770280793647</v>
+        <v>3.547364813490225</v>
       </c>
     </row>
     <row r="19">
@@ -2077,13 +2077,13 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3963285464173486</v>
+        <v>0.3961073401413146</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3801911881083933</v>
+        <v>0.3802938556685332</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2234802654742581</v>
+        <v>0.223598804190152</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>0.6036714535826514</v>
+        <v>0.6038926598586853</v>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>18.11014360747954</v>
+        <v>4.075852263582984</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.11014360747954</v>
+        <v>4.075852263582984</v>
       </c>
     </row>
     <row r="20">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>16.92718591597675</v>
+        <v>3.808221428394718</v>
       </c>
       <c r="AB20" t="n">
-        <v>16.92718591597675</v>
+        <v>3.808221428394718</v>
       </c>
     </row>
     <row r="21">
@@ -2233,13 +2233,13 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4748223715979581</v>
+        <v>0.4748223715979583</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4821446094511965</v>
+        <v>0.4821446094511964</v>
       </c>
       <c r="S21" t="n">
-        <v>0.04303301895084537</v>
+        <v>0.04303301895084536</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>0.5178553905488035</v>
+        <v>0.5178553905488036</v>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>15.53566171646411</v>
+        <v>3.495160988164534</v>
       </c>
       <c r="AB21" t="n">
-        <v>15.53566171646411</v>
+        <v>3.495160988164534</v>
       </c>
     </row>
     <row r="22">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>19.2927560909328</v>
+        <v>4.34041946032726</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.2927560909328</v>
+        <v>4.34041946032726</v>
       </c>
     </row>
     <row r="23">
@@ -2389,13 +2389,13 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4069732312491904</v>
+        <v>0.406988013196621</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3643269271489426</v>
+        <v>0.3644240071799103</v>
       </c>
       <c r="S23" t="n">
-        <v>0.228699841601867</v>
+        <v>0.2285879796234687</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
-        <v>0.5930267687508096</v>
+        <v>0.593011986803379</v>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>17.79080306252429</v>
+        <v>4.002415345319804</v>
       </c>
       <c r="AB23" t="n">
-        <v>17.79080306252429</v>
+        <v>4.002415345319804</v>
       </c>
     </row>
     <row r="24">
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>18.8039106225782</v>
+        <v>4.230440648905065</v>
       </c>
       <c r="AB24" t="n">
-        <v>18.8039106225782</v>
+        <v>4.230440648905065</v>
       </c>
     </row>
     <row r="25">
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>15.79988457924637</v>
+        <v>3.554604960299884</v>
       </c>
       <c r="AB25" t="n">
-        <v>15.79988457924637</v>
+        <v>3.554604960299884</v>
       </c>
     </row>
     <row r="26">
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>17.28335731475585</v>
+        <v>3.88835167330044</v>
       </c>
       <c r="AB26" t="n">
-        <v>17.28335731475585</v>
+        <v>3.88835167330044</v>
       </c>
     </row>
     <row r="27">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>16.36700648597252</v>
+        <v>3.682194141893745</v>
       </c>
       <c r="AB27" t="n">
-        <v>16.36700648597252</v>
+        <v>3.682194141893745</v>
       </c>
     </row>
     <row r="28">
@@ -2769,55 +2769,55 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
         <v>2.55</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3387880751782242</v>
+        <v>0.3445218492716909</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2892093324692158</v>
+        <v>0.2906903103229892</v>
       </c>
       <c r="N28" t="n">
-        <v>0.37200259235256</v>
+        <v>0.3647878404053199</v>
       </c>
       <c r="O28" t="n">
-        <v>0.05417776866844304</v>
+        <v>0.07502723311546844</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3380050469588385</v>
+        <v>0.3380679964157302</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3739226193959451</v>
+        <v>0.3740222378372361</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2880723336452164</v>
+        <v>0.2879097657470336</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08471328692672925</v>
+        <v>0.08333192751424695</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.08471328692672925</v>
+        <v>0.08333192751424695</v>
       </c>
       <c r="X28" t="n">
-        <v>0.3739226193959451</v>
+        <v>0.3740222378372361</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>11.21767858187835</v>
+        <v>2.524388001463713</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.21767858187835</v>
+        <v>2.524388001463713</v>
       </c>
     </row>
     <row r="29">
@@ -2867,25 +2867,25 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4803482268595571</v>
+        <v>0.4882740930743861</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2830623479708104</v>
+        <v>0.2854525467204104</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2365894251696326</v>
+        <v>0.2262733602052034</v>
       </c>
       <c r="O29" t="n">
-        <v>0.05142577157502526</v>
+        <v>0.07791053619038224</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>1.3266</v>
+        <v>1.298333333333333</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -2947,25 +2947,25 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3674925475248008</v>
+        <v>0.3717001055966209</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2962908664418707</v>
+        <v>0.2903907074973601</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3362165860333284</v>
+        <v>0.337909186906019</v>
       </c>
       <c r="O30" t="n">
-        <v>0.05470682830282048</v>
+        <v>0.07613636363636367</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2983,19 +2983,19 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0.01156614655856542</v>
+        <v>0.00735858848674531</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>0.01156614655856542</v>
+        <v>0.00735858848674531</v>
       </c>
       <c r="X30" t="n">
         <v>0.3790586940833662</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>11.37176082250099</v>
+        <v>2.55838055172261</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.37176082250099</v>
+        <v>2.55838055172261</v>
       </c>
     </row>
     <row r="31">
@@ -3045,25 +3045,25 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="J31" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5001539461530566</v>
+        <v>0.5038814396612561</v>
       </c>
       <c r="M31" t="n">
-        <v>0.276247819096165</v>
+        <v>0.2741707833450953</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2235982347507783</v>
+        <v>0.2219477769936486</v>
       </c>
       <c r="O31" t="n">
-        <v>0.05230758153934767</v>
+        <v>0.07275342569460208</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -3081,19 +3081,19 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.04184625919975826</v>
+        <v>-0.04557375270795772</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.04184625919975826</v>
+        <v>-0.04557375270795772</v>
       </c>
       <c r="X31" t="n">
         <v>0.4583076869532984</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>13.74923060859895</v>
+        <v>3.09325571819867</v>
       </c>
       <c r="AB31" t="n">
-        <v>13.74923060859895</v>
+        <v>3.09325571819867</v>
       </c>
     </row>
     <row r="32">
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="J32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3578448399158204</v>
+        <v>0.3565379226699568</v>
       </c>
       <c r="M32" t="n">
-        <v>0.301044071675214</v>
+        <v>0.3024821731038665</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3411110884089655</v>
+        <v>0.3409799042261768</v>
       </c>
       <c r="O32" t="n">
-        <v>0.05453103824218264</v>
+        <v>0.06644514567978321</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -3179,19 +3179,19 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.07333447441702423</v>
+        <v>0.0718963729883717</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.07333447441702423</v>
+        <v>0.0718963729883717</v>
       </c>
       <c r="X32" t="n">
         <v>0.3743785460922382</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>11.23135638276715</v>
+        <v>2.526792832494484</v>
       </c>
       <c r="AB32" t="n">
-        <v>11.23135638276715</v>
+        <v>2.526792832494484</v>
       </c>
     </row>
     <row r="33">
@@ -3241,55 +3241,55 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="J33" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="K33" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3338384652587457</v>
+        <v>0.337909186906019</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2838626471062389</v>
+        <v>0.2903907074973601</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3822988876350153</v>
+        <v>0.3717001055966209</v>
       </c>
       <c r="O33" t="n">
-        <v>0.05473968011274155</v>
+        <v>0.07613636363636367</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3082132045474408</v>
+        <v>0.3082132045474411</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3596842295085814</v>
+        <v>0.359684229508581</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3321025659439776</v>
+        <v>0.3321025659439781</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0.07582158240234249</v>
+        <v>0.06929352201122096</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.07582158240234249</v>
+        <v>0.06929352201122096</v>
       </c>
       <c r="X33" t="n">
-        <v>0.3596842295085814</v>
+        <v>0.359684229508581</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>10.79052688525744</v>
+        <v>2.427616492905725</v>
       </c>
       <c r="AB33" t="n">
-        <v>10.79052688525744</v>
+        <v>2.427616492905725</v>
       </c>
     </row>
     <row r="34">
@@ -3339,25 +3339,25 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="J34" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5010799503392914</v>
+        <v>0.5008809239913865</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2759570740998997</v>
+        <v>0.2851168336566354</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2229629755608089</v>
+        <v>0.2140022423519781</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0503628994081784</v>
+        <v>0.0791797304499382</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -3371,7 +3371,7 @@
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>1.314910858995138</v>
+        <v>1.296197411003236</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -3417,25 +3417,25 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="L35" t="n">
-        <v>0.302817041016593</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2925678488591084</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4046151101242987</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05169556016554244</v>
+        <v>0.07954545454545459</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3453,19 +3453,19 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08208038428301917</v>
+        <v>0.0851745489316012</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.08208038428301917</v>
+        <v>0.0851745489316012</v>
       </c>
       <c r="X35" t="n">
         <v>0.3746482331421275</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>11.23944699426383</v>
+        <v>2.528613031092374</v>
       </c>
       <c r="AB35" t="n">
-        <v>11.23944699426383</v>
+        <v>2.528613031092374</v>
       </c>
     </row>
     <row r="36">
@@ -3515,25 +3515,25 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3720103701359559</v>
+        <v>0.3717001055966209</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2927859394588541</v>
+        <v>0.2903907074973601</v>
       </c>
       <c r="N36" t="n">
-        <v>0.3352036904051899</v>
+        <v>0.337909186906019</v>
       </c>
       <c r="O36" t="n">
-        <v>0.05415572851310402</v>
+        <v>0.07613636363636367</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -3551,19 +3551,19 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0.02233927582102341</v>
+        <v>0.02264954036035843</v>
       </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.02233927582102341</v>
+        <v>0.02264954036035843</v>
       </c>
       <c r="X36" t="n">
         <v>0.3943496459569794</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>11.83048937870938</v>
+        <v>2.661583761413864</v>
       </c>
       <c r="AB36" t="n">
-        <v>11.83048937870938</v>
+        <v>2.661583761413864</v>
       </c>
     </row>
     <row r="37">
@@ -3613,25 +3613,25 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="J37" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="K37" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3661612260661003</v>
+        <v>0.3636557534392663</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2927029554046913</v>
+        <v>0.2991361842806867</v>
       </c>
       <c r="N37" t="n">
-        <v>0.3411358185292085</v>
+        <v>0.3372080622800468</v>
       </c>
       <c r="O37" t="n">
-        <v>0.05445459162485533</v>
+        <v>0.07837387154275222</v>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -3647,7 +3647,7 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="n">
-        <v>1.340819366852886</v>
+        <v>1.32311320754717</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>

--- a/p6_deployment/data/italy/predicciones.xlsx
+++ b/p6_deployment/data/italy/predicciones.xlsx
@@ -605,52 +605,52 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="L2" t="n">
-        <v>0.158004158004158</v>
+        <v>0.1649473486776882</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2494802494802495</v>
+        <v>0.2495913828675545</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5925155925155925</v>
+        <v>0.5854612684547574</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05482456140350878</v>
+        <v>0.05435488883238682</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2322024601791497</v>
+        <v>0.2287387667007373</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5231222758917055</v>
+        <v>0.5359146990191095</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2446752639291447</v>
+        <v>0.2353465342801532</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.273642026411456</v>
+        <v>0.286323316151555</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.273642026411456</v>
+        <v>0.286323316151555</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5231222758917055</v>
+        <v>0.5359146990191095</v>
       </c>
       <c r="Y2" t="n">
         <v>3.8</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>3.530708773348613</v>
+        <v>6.408519536582851</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.530708773348613</v>
+        <v>6.408519536582851</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2711379192563951</v>
+        <v>0.2725231151948335</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3958014781491829</v>
+        <v>0.3956846156670256</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3330606025944221</v>
+        <v>0.3317922691381407</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1009831338966516</v>
+        <v>0.1008662714144943</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1009831338966516</v>
+        <v>0.1008662714144943</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3958014781491829</v>
+        <v>0.3956846156670256</v>
       </c>
       <c r="Y3" t="n">
         <v>3.2</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>2.671382611309341</v>
+        <v>4.731634706920012</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.671382611309341</v>
+        <v>4.731634706920012</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4372196027838811</v>
+        <v>0.4400086634656995</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5004885127723747</v>
+        <v>0.4942897790766149</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06229188444374419</v>
+        <v>0.06570155745768574</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2237053833631196</v>
+        <v>0.2175066496673598</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2237053833631196</v>
+        <v>0.2175066496673598</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5004885127723747</v>
+        <v>0.4942897790766149</v>
       </c>
       <c r="Y4" t="n">
         <v>3.4</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>3.377946733377945</v>
+        <v>5.910764738760704</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.377946733377945</v>
+        <v>5.910764738760704</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3446007529713776</v>
+        <v>0.3447548041594359</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3526910107122487</v>
+        <v>0.3527536688143402</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3027082363163736</v>
+        <v>0.3024915270262238</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05857336365342514</v>
+        <v>0.05863602175551663</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05857336365342514</v>
+        <v>0.05863602175551663</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3526910107122487</v>
+        <v>0.3527536688143402</v>
       </c>
       <c r="Y5" t="n">
         <v>3.2</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>2.380417166675411</v>
+        <v>4.218262313639893</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.380417166675411</v>
+        <v>4.218262313639893</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4323588882589248</v>
+        <v>0.4272144406220799</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3773943291766953</v>
+        <v>0.3766028498451762</v>
       </c>
       <c r="S6" t="n">
-        <v>0.19024678256438</v>
+        <v>0.1961827095327438</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.07893478087621114</v>
+        <v>-0.0840792285130561</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.07893478087621114</v>
+        <v>-0.0840792285130561</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4323588882589248</v>
+        <v>0.4272144406220799</v>
       </c>
       <c r="Y6" t="n">
         <v>1.85</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>2.918119511177259</v>
+        <v>5.108671387532308</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.918119511177259</v>
+        <v>5.108671387532308</v>
       </c>
     </row>
     <row r="7">
@@ -1119,28 +1119,28 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2317021112264667</v>
+        <v>0.2314049743946865</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5192890211216494</v>
+        <v>0.5173633450324683</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2490088676518839</v>
+        <v>0.2512316805728451</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2317692738862625</v>
+        <v>0.2298435977970813</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2317692738862625</v>
+        <v>0.2298435977970813</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5192890211216494</v>
+        <v>0.5173633450324683</v>
       </c>
       <c r="Y7" t="n">
         <v>3.3</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>3.504836989884513</v>
+        <v>6.186680660599315</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.504836989884513</v>
+        <v>6.186680660599315</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2446428108738781</v>
+        <v>0.243982251206936</v>
       </c>
       <c r="R8" t="n">
-        <v>0.492293700379923</v>
+        <v>0.4947117110728264</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2630634887461987</v>
+        <v>0.2613060377202377</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.215697955699072</v>
+        <v>0.2181159663919753</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.215697955699072</v>
+        <v>0.2181159663919753</v>
       </c>
       <c r="X8" t="n">
-        <v>0.492293700379923</v>
+        <v>0.4947117110728264</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>3.322637492415771</v>
+        <v>5.915810242169697</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.322637492415771</v>
+        <v>5.915810242169697</v>
       </c>
     </row>
     <row r="9">
@@ -1312,34 +1312,34 @@
         <v>0.05900900900900896</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4672142682244892</v>
+        <v>0.4688481526967667</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4687109776100618</v>
+        <v>0.4645031770758087</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06407475416544899</v>
+        <v>0.06664867022742459</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2326412200600831</v>
+        <v>-0.1691782190599326</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2326412200600831</v>
+        <v>-0.1691782190599326</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4687109776100618</v>
+        <v>0.4688481526967667</v>
       </c>
       <c r="Y9" t="n">
-        <v>4</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>3.163470639807426</v>
+        <v>5.606531322517188</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.163470639807426</v>
+        <v>5.606531322517188</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2653946255938225</v>
+        <v>0.2651006284586224</v>
       </c>
       <c r="R10" t="n">
-        <v>0.406166107039758</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3284392673664195</v>
+        <v>0.3281732089376114</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.149916107039758</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.149916107039758</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="X10" t="n">
-        <v>0.406166107039758</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="Y10" t="n">
         <v>3.7</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>2.74133659308937</v>
+        <v>4.8636705876072</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.74133659308937</v>
+        <v>4.8636705876072</v>
       </c>
     </row>
     <row r="11">
@@ -1511,28 +1511,28 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4896822687582531</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4535486110547644</v>
+        <v>0.4566736230579956</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05676912018698233</v>
+        <v>0.05435846129682308</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2215552845845635</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2215552845845635</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4896822687582531</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="Y11" t="n">
         <v>1.33</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>3.305012158985048</v>
+        <v>5.847125383777921</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.305012158985048</v>
+        <v>5.847125383777921</v>
       </c>
     </row>
     <row r="12">
@@ -1584,13 +1584,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5010684547933092</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2696927271387518</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.229238818067939</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.09056573449051752</v>
+      </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1602,7 +1616,9 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>1.25557461406518</v>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -1646,13 +1662,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2216320651496475</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.247988310735011</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5303796241153415</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.08985084607100191</v>
+      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1664,7 +1694,9 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>1.220136286201022</v>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -1676,20 +1708,20 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45508.54166666666</v>
+        <v>45508.64583333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>padova</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1708,13 +1740,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6227621063893677</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2288650740980926</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1483728195125398</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.09234666313851303</v>
+      </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1726,7 +1772,9 @@
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>1.187159685863874</v>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -1738,20 +1786,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45508.65625</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>padova</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1770,13 +1818,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2902468687989416</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2997631595792349</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.4099899716218234</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.09375966319287654</v>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1788,7 +1850,9 @@
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>1.305669144981413</v>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -1843,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4714480047822971</v>
+        <v>0.4694967552742121</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4056032949254636</v>
+        <v>0.4042830898537844</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1229487002922391</v>
+        <v>0.1262201548720035</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1860,7 +1924,7 @@
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>0.5285519952177029</v>
+        <v>0.5305032447257878</v>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
@@ -1869,10 +1933,10 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>3.567355573809254</v>
+        <v>6.343808845453178</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.567355573809254</v>
+        <v>6.343808845453178</v>
       </c>
     </row>
     <row r="17">
@@ -1921,13 +1985,13 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.474807650426295</v>
+        <v>0.4727240812949189</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4097372930966371</v>
+        <v>0.4071627836349588</v>
       </c>
       <c r="S17" t="n">
-        <v>0.115455056477068</v>
+        <v>0.1201131350701222</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -1938,7 +2002,7 @@
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
-        <v>0.525192349573705</v>
+        <v>0.5272759187050811</v>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
@@ -1947,10 +2011,10 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>3.544680320054506</v>
+        <v>6.305216170364257</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.544680320054506</v>
+        <v>6.305216170364257</v>
       </c>
     </row>
     <row r="18">
@@ -1999,13 +2063,13 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4744099064021176</v>
+        <v>0.4738402187299073</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3974162014452964</v>
+        <v>0.3970833715775151</v>
       </c>
       <c r="S18" t="n">
-        <v>0.128173892152586</v>
+        <v>0.1290764096925773</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -2016,7 +2080,7 @@
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>0.5255900935978823</v>
+        <v>0.5261597812700927</v>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
@@ -2025,10 +2089,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>3.547364813490225</v>
+        <v>6.291869291521921</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.547364813490225</v>
+        <v>6.291869291521921</v>
       </c>
     </row>
     <row r="19">
@@ -2077,13 +2141,13 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3961073401413146</v>
+        <v>0.3997746834822209</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3802938556685332</v>
+        <v>0.3808697754406668</v>
       </c>
       <c r="S19" t="n">
-        <v>0.223598804190152</v>
+        <v>0.2193555410771125</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
@@ -2094,7 +2158,7 @@
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>0.6038926598586853</v>
+        <v>0.6002253165177791</v>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
@@ -2103,10 +2167,10 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>4.075852263582984</v>
+        <v>7.177552088599557</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.075852263582984</v>
+        <v>7.177552088599557</v>
       </c>
     </row>
     <row r="20">
@@ -2155,13 +2219,13 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4357604694674418</v>
+        <v>0.4375459700908128</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3721789459378736</v>
+        <v>0.3730150628421344</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1920605845946844</v>
+        <v>0.1894389670670526</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2172,7 +2236,7 @@
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>0.5642395305325583</v>
+        <v>0.5624540299091871</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
@@ -2181,10 +2245,10 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>3.808221428394718</v>
+        <v>6.725879408980817</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.808221428394718</v>
+        <v>6.725879408980817</v>
       </c>
     </row>
     <row r="21">
@@ -2233,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4748223715979583</v>
+        <v>0.4762256520660549</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4821446094511964</v>
+        <v>0.4803533188099261</v>
       </c>
       <c r="S21" t="n">
-        <v>0.04303301895084536</v>
+        <v>0.0434210291240188</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -2250,7 +2314,7 @@
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>0.5178553905488036</v>
+        <v>0.519646681190074</v>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
@@ -2259,10 +2323,10 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>3.495160988164534</v>
+        <v>6.213985014074568</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.495160988164534</v>
+        <v>6.213985014074568</v>
       </c>
     </row>
     <row r="22">
@@ -2311,13 +2375,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3378760736066398</v>
+        <v>0.3405749389402209</v>
       </c>
       <c r="R22" t="n">
-        <v>0.35690813030224</v>
+        <v>0.3558480852076204</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3052157960911198</v>
+        <v>0.3035769758521589</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
@@ -2328,7 +2392,7 @@
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
-        <v>0.64309186969776</v>
+        <v>0.6441519147923795</v>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr">
@@ -2337,10 +2401,10 @@
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>4.34041946032726</v>
+        <v>7.702830577384516</v>
       </c>
       <c r="AB22" t="n">
-        <v>4.34041946032726</v>
+        <v>7.702830577384516</v>
       </c>
     </row>
     <row r="23">
@@ -2389,13 +2453,13 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.406988013196621</v>
+        <v>0.403847330668933</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3644240071799103</v>
+        <v>0.3641302640579551</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2285879796234687</v>
+        <v>0.232022405273112</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
@@ -2406,7 +2470,7 @@
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
-        <v>0.593011986803379</v>
+        <v>0.596152669331067</v>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr">
@@ -2415,10 +2479,10 @@
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>4.002415345319804</v>
+        <v>7.128850981670743</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.002415345319804</v>
+        <v>7.128850981670743</v>
       </c>
     </row>
     <row r="24">
@@ -2467,13 +2531,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3694937315310033</v>
+        <v>0.3742469639595186</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3732029792473935</v>
+        <v>0.3749425523620097</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2573032892216031</v>
+        <v>0.2508104836784718</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
@@ -2484,7 +2548,7 @@
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
-        <v>0.6267970207526066</v>
+        <v>0.6250574476379902</v>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr">
@@ -2493,10 +2557,10 @@
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>4.230440648905065</v>
+        <v>7.474497101882698</v>
       </c>
       <c r="AB24" t="n">
-        <v>4.230440648905065</v>
+        <v>7.474497101882698</v>
       </c>
     </row>
     <row r="25">
@@ -2545,13 +2609,13 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4733371806917877</v>
+        <v>0.4739942378041332</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4239851741582934</v>
+        <v>0.422798329895286</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1026776451499188</v>
+        <v>0.1032074323005807</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
@@ -2562,7 +2626,7 @@
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
-        <v>0.5266628193082123</v>
+        <v>0.5260057621958667</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
@@ -2571,10 +2635,10 @@
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>3.554604960299884</v>
+        <v>6.290027516612613</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.554604960299884</v>
+        <v>6.290027516612613</v>
       </c>
     </row>
     <row r="26">
@@ -2623,13 +2687,13 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4238880895081383</v>
+        <v>0.4214803559717588</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3826738469226045</v>
+        <v>0.3823090013622199</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1934380635692574</v>
+        <v>0.196210642666021</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
@@ -2640,7 +2704,7 @@
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
-        <v>0.5761119104918617</v>
+        <v>0.5785196440282412</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
@@ -2649,10 +2713,10 @@
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>3.88835167330044</v>
+        <v>6.917993568449856</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.88835167330044</v>
+        <v>6.917993568449856</v>
       </c>
     </row>
     <row r="27">
@@ -2701,13 +2765,13 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4544331171342493</v>
+        <v>0.4455732802592645</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3913317838444145</v>
+        <v>0.3852067815535028</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1542350990213361</v>
+        <v>0.1692199381872326</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
@@ -2718,7 +2782,7 @@
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>0.5455668828657507</v>
+        <v>0.5544267197407355</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
@@ -2727,10 +2791,10 @@
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>3.682194141893745</v>
+        <v>6.629888061598689</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.682194141893745</v>
+        <v>6.629888061598689</v>
       </c>
     </row>
     <row r="28">
@@ -2793,28 +2857,28 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3380679964157302</v>
+        <v>0.3388659580677731</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3740222378372361</v>
+        <v>0.3746946149815555</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2879097657470336</v>
+        <v>0.2864394269506713</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08333192751424695</v>
+        <v>0.08400430465856634</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.08333192751424695</v>
+        <v>0.08400430465856634</v>
       </c>
       <c r="X28" t="n">
-        <v>0.3740222378372361</v>
+        <v>0.3746946149815555</v>
       </c>
       <c r="Y28" t="n">
         <v>3.2</v>
@@ -2825,10 +2889,10 @@
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>2.524388001463713</v>
+        <v>4.480634259065295</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.524388001463713</v>
+        <v>4.480634259065295</v>
       </c>
     </row>
     <row r="29">
@@ -2971,28 +3035,28 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3790586940833662</v>
+        <v>0.3771596572542751</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3715543510497629</v>
+        <v>0.3703923812577244</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2493869548668708</v>
+        <v>0.2524479614880006</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0.00735858848674531</v>
+        <v>0.00545955165765416</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>0.00735858848674531</v>
+        <v>0.00545955165765416</v>
       </c>
       <c r="X30" t="n">
-        <v>0.3790586940833662</v>
+        <v>0.3771596572542751</v>
       </c>
       <c r="Y30" t="n">
         <v>2.5</v>
@@ -3003,10 +3067,10 @@
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>2.55838055172261</v>
+        <v>4.510111471748842</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.55838055172261</v>
+        <v>4.510111471748842</v>
       </c>
     </row>
     <row r="31">
@@ -3069,28 +3133,28 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4583076869532984</v>
+        <v>0.451102352483415</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3950426087473192</v>
+        <v>0.3894999314195416</v>
       </c>
       <c r="S31" t="n">
-        <v>0.146649704299382</v>
+        <v>0.1593977160970436</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.04557375270795772</v>
+        <v>-0.05277908717784108</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.04557375270795772</v>
+        <v>-0.05277908717784108</v>
       </c>
       <c r="X31" t="n">
-        <v>0.4583076869532984</v>
+        <v>0.451102352483415</v>
       </c>
       <c r="Y31" t="n">
         <v>1.85</v>
@@ -3101,10 +3165,10 @@
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>3.09325571819867</v>
+        <v>5.394325336065033</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.09325571819867</v>
+        <v>5.394325336065033</v>
       </c>
     </row>
     <row r="32">
@@ -3167,28 +3231,28 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.3614264383835507</v>
+        <v>0.3613841827993978</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3743785460922382</v>
+        <v>0.3730405837229831</v>
       </c>
       <c r="S32" t="n">
-        <v>0.2641950155242111</v>
+        <v>0.265575233477619</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.0718963729883717</v>
+        <v>0.07055841061911661</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.0718963729883717</v>
+        <v>0.07055841061911661</v>
       </c>
       <c r="X32" t="n">
-        <v>0.3743785460922382</v>
+        <v>0.3730405837229831</v>
       </c>
       <c r="Y32" t="n">
         <v>3.1</v>
@@ -3199,10 +3263,10 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>2.526792832494484</v>
+        <v>4.460855194124398</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.526792832494484</v>
+        <v>4.460855194124398</v>
       </c>
     </row>
     <row r="33">
@@ -3265,28 +3329,28 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3082132045474411</v>
+        <v>0.310221098231573</v>
       </c>
       <c r="R33" t="n">
-        <v>0.359684229508581</v>
+        <v>0.357962016962774</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3321025659439781</v>
+        <v>0.3318168848056527</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0.06929352201122096</v>
+        <v>0.06757130946541395</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.06929352201122096</v>
+        <v>0.06757130946541395</v>
       </c>
       <c r="X33" t="n">
-        <v>0.359684229508581</v>
+        <v>0.357962016962774</v>
       </c>
       <c r="Y33" t="n">
         <v>3.2</v>
@@ -3297,10 +3361,10 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>2.427616492905725</v>
+        <v>4.280544241946123</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.427616492905725</v>
+        <v>4.280544241946123</v>
       </c>
     </row>
     <row r="34">
@@ -3441,28 +3505,28 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3272688283754523</v>
+        <v>0.3271006089805857</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3746482331421275</v>
+        <v>0.3762116784915401</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2980829384824198</v>
+        <v>0.2966877125278745</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0851745489316012</v>
+        <v>0.08673799428101381</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.0851745489316012</v>
+        <v>0.08673799428101381</v>
       </c>
       <c r="X35" t="n">
-        <v>0.3746482331421275</v>
+        <v>0.3762116784915401</v>
       </c>
       <c r="Y35" t="n">
         <v>3.2</v>
@@ -3473,10 +3537,10 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>2.528613031092374</v>
+        <v>4.498775450489541</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.528613031092374</v>
+        <v>4.498775450489541</v>
       </c>
     </row>
     <row r="36">
@@ -3536,34 +3600,34 @@
         <v>0.07613636363636367</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3943496459569794</v>
+        <v>0.3792582472531151</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3799057602844827</v>
+        <v>0.3804626357347388</v>
       </c>
       <c r="S36" t="n">
-        <v>0.2257445937585379</v>
+        <v>0.2402791170121459</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0.02264954036035843</v>
+        <v>0.09007192823737875</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.02264954036035843</v>
+        <v>0.09007192823737875</v>
       </c>
       <c r="X36" t="n">
-        <v>0.3943496459569794</v>
+        <v>0.3804626357347388</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3571,10 +3635,10 @@
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>2.661583761413864</v>
+        <v>4.549608806230817</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.661583761413864</v>
+        <v>4.549608806230817</v>
       </c>
     </row>
     <row r="37">
